--- a/public/用語集登録テンプレート.xlsx
+++ b/public/用語集登録テンプレート.xlsx
@@ -398,31 +398,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ja</v>
       </c>
       <c r="B1" t="str">
+        <v>yomi</v>
+      </c>
+      <c r="C1" t="str">
         <v>en</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>zh</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>zh-TW</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>ko</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>fr</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>es</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>th</v>
       </c>
     </row>
@@ -451,6 +465,9 @@
       <c r="H2" t="str">
         <v/>
       </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -477,6 +494,9 @@
       <c r="H3" t="str">
         <v/>
       </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -503,6 +523,9 @@
       <c r="H4" t="str">
         <v/>
       </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -529,6 +552,9 @@
       <c r="H5" t="str">
         <v/>
       </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -555,6 +581,9 @@
       <c r="H6" t="str">
         <v/>
       </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -581,6 +610,9 @@
       <c r="H7" t="str">
         <v/>
       </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -607,6 +639,9 @@
       <c r="H8" t="str">
         <v/>
       </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -633,6 +668,9 @@
       <c r="H9" t="str">
         <v/>
       </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -659,6 +697,9 @@
       <c r="H10" t="str">
         <v/>
       </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -685,6 +726,9 @@
       <c r="H11" t="str">
         <v/>
       </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -711,6 +755,9 @@
       <c r="H12" t="str">
         <v/>
       </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -737,6 +784,9 @@
       <c r="H13" t="str">
         <v/>
       </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -763,6 +813,9 @@
       <c r="H14" t="str">
         <v/>
       </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -789,6 +842,9 @@
       <c r="H15" t="str">
         <v/>
       </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -815,6 +871,9 @@
       <c r="H16" t="str">
         <v/>
       </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -841,6 +900,9 @@
       <c r="H17" t="str">
         <v/>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -867,6 +929,9 @@
       <c r="H18" t="str">
         <v/>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -893,6 +958,9 @@
       <c r="H19" t="str">
         <v/>
       </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -919,24 +987,32 @@
       <c r="H20" t="str">
         <v/>
       </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="66.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>列名</v>
       </c>
       <c r="B1" t="str">
-        <v>言語</v>
+        <v>説明</v>
       </c>
       <c r="C1" t="str">
         <v>必須</v>
@@ -947,7 +1023,7 @@
         <v>ja</v>
       </c>
       <c r="B2" t="str">
-        <v>日本語（STT認識・翻訳のキー）</v>
+        <v>日本語（音声認識・翻訳のキー）</v>
       </c>
       <c r="C2" t="str">
         <v>○</v>
@@ -955,21 +1031,21 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>en</v>
+        <v>yomi</v>
       </c>
       <c r="B3" t="str">
-        <v>英語訳</v>
+        <v>よみ（ひらがな）。難読な駅名など、漢字にならず読みで出てしまう語を漢字へ補正するために使用</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>任意</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>zh</v>
+        <v>en</v>
       </c>
       <c r="B4" t="str">
-        <v>中国語訳（簡体）</v>
+        <v>英語訳</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -977,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>zh-TW</v>
+        <v>zh</v>
       </c>
       <c r="B5" t="str">
-        <v>中国語訳（繁体）</v>
+        <v>中国語訳（簡体）</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -988,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ko</v>
+        <v>zh-TW</v>
       </c>
       <c r="B6" t="str">
-        <v>韓国語訳</v>
+        <v>中国語訳（繁体）</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -999,10 +1075,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>fr</v>
+        <v>ko</v>
       </c>
       <c r="B7" t="str">
-        <v>フランス語訳</v>
+        <v>韓国語訳</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -1010,10 +1086,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>es</v>
+        <v>fr</v>
       </c>
       <c r="B8" t="str">
-        <v>スペイン語訳</v>
+        <v>フランス語訳</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -1021,10 +1097,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>th</v>
+        <v>es</v>
       </c>
       <c r="B9" t="str">
-        <v>タイ語訳</v>
+        <v>スペイン語訳</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -1032,40 +1108,62 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>th</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>タイ語訳</v>
       </c>
       <c r="C10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>【入力例】ja: Suica　en: Suica (IC card)　zh: 西瓜卡　zh-TW: 西瓜卡　ko: 스이카</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>※ 「用語集」シートの2行目から実際のデータを入力してください。1行目（列名）は変更しないでください。</v>
+        <v>【入力例】ja: 舎人 / yomi: とねり / en: Toneri</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>【入力例】ja: 定期券 / yomi:（空欄でOK） / en: commuter pass</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>※「用語集」シートの2行目から入力してください。1行目（列名）は変更しないでください。</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>※ yomi は任意です。難しい読みの駅名・地名で、音声認識が漢字にならない場合に、ひらがなの読みを入れてください。</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/用語集登録テンプレート.xlsx
+++ b/public/用語集登録テンプレート.xlsx
@@ -1034,10 +1034,10 @@
         <v>yomi</v>
       </c>
       <c r="B3" t="str">
-        <v>よみ（ひらがな）。難読な駅名など、漢字にならず読みで出てしまう語を漢字へ補正するために使用</v>
+        <v>よみ（ひらがな）。認識した文字を登録どおりの表記に直すために使用。英字を含む語（SUICA など）は読み上げにも使われます</v>
       </c>
       <c r="C3" t="str">
-        <v>任意</v>
+        <v>○</v>
       </c>
     </row>
     <row r="4">
@@ -1130,7 +1130,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>【入力例】ja: 定期券 / yomi:（空欄でOK） / en: commuter pass</v>
+        <v>【入力例】ja: 定期券 / yomi: ていきけん / en: commuter pass</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>※ yomi は任意です。難しい読みの駅名・地名で、音声認識が漢字にならない場合に、ひらがなの読みを入れてください。</v>
+        <v>※ yomi は必須です。すべての語にひらがなの読みを入れてください。未入力の行は登録されません。</v>
       </c>
       <c r="B15" t="str">
         <v/>
